--- a/results/05_transient_transcription_output/508/508_198802_SF.JPG_stage_correct_values.xlsx
+++ b/results/05_transient_transcription_output/508/508_198802_SF.JPG_stage_correct_values.xlsx
@@ -26,7 +26,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -35,8 +35,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FF9933"/>
-        <bgColor rgb="00FF9933"/>
+        <fgColor rgb="FF6DCD57"/>
+        <bgColor rgb="FF6DCD57"/>
       </patternFill>
     </fill>
     <fill>
@@ -49,12 +49,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00CC3300"/>
         <bgColor rgb="00CC3300"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6DCD57"/>
-        <bgColor rgb="FF6DCD57"/>
       </patternFill>
     </fill>
     <fill>
@@ -158,7 +152,7 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -167,7 +161,7 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -781,13 +775,13 @@
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr"/>
-      <c r="D4" s="3" t="n">
-        <v>39.7</v>
-      </c>
-      <c r="E4" s="3" t="n">
+      <c r="D4" s="8" t="n">
+        <v>31.7</v>
+      </c>
+      <c r="E4" s="8" t="n">
         <v>16.9</v>
       </c>
-      <c r="F4" s="3" t="n">
+      <c r="F4" s="8" t="n">
         <v>24.3</v>
       </c>
       <c r="G4" s="3" t="n">
@@ -805,14 +799,14 @@
       <c r="K4" s="3" t="n">
         <v>18.9</v>
       </c>
-      <c r="L4" s="3" t="n">
+      <c r="L4" s="8" t="n">
         <v>18.4</v>
       </c>
-      <c r="M4" s="11" t="n">
+      <c r="M4" s="8" t="n">
         <v>18.4</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>28.8</v>
+        <v>21.1</v>
       </c>
       <c r="O4" s="3" t="n">
         <v>91.2</v>
@@ -820,25 +814,25 @@
       <c r="P4" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="Q4" s="11" t="n">
+      <c r="Q4" s="8" t="n">
         <v>30.6</v>
       </c>
       <c r="R4" s="3" t="n">
-        <v>23.8</v>
+        <v>29.8</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>2.5</v>
+        <v>25.3</v>
       </c>
       <c r="T4" s="3" t="n">
-        <v>4.5</v>
+        <v>45.2</v>
       </c>
       <c r="U4" s="3" t="n">
         <v>18.6</v>
       </c>
-      <c r="V4" s="3" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="W4" s="11" t="n">
+      <c r="V4" s="8" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="W4" s="8" t="n">
         <v>24.9</v>
       </c>
       <c r="X4" s="3" t="inlineStr"/>
@@ -858,17 +852,17 @@
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr"/>
-      <c r="D5" s="11" t="n">
+      <c r="D5" s="8" t="n">
         <v>26.2</v>
       </c>
-      <c r="E5" s="11" t="n">
+      <c r="E5" s="8" t="n">
         <v>17.4</v>
       </c>
-      <c r="F5" s="11" t="n">
+      <c r="F5" s="8" t="n">
         <v>21.8</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>81.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H5" s="3" t="n">
         <v>17.3</v>
@@ -882,29 +876,29 @@
       <c r="K5" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="L5" s="3" t="n">
-        <v>11.6</v>
-      </c>
-      <c r="M5" s="11" t="n">
+      <c r="L5" s="8" t="n">
         <v>17.6</v>
       </c>
+      <c r="M5" s="8" t="n">
+        <v>17.6</v>
+      </c>
       <c r="N5" s="3" t="n">
-        <v>2</v>
+        <v>20.1</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>91.2</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="P5" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="Q5" s="11" t="n">
+      <c r="Q5" s="8" t="n">
         <v>23.9</v>
       </c>
       <c r="R5" s="3" t="n">
         <v>21</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>23.1</v>
+        <v>28.1</v>
       </c>
       <c r="T5" s="3" t="n">
         <v>70.2</v>
@@ -912,17 +906,17 @@
       <c r="U5" s="3" t="n">
         <v>6.5</v>
       </c>
-      <c r="V5" s="3" t="n">
+      <c r="V5" s="8" t="n">
         <v>23.1</v>
       </c>
-      <c r="W5" s="11" t="n">
+      <c r="W5" s="8" t="n">
         <v>21.3</v>
       </c>
       <c r="X5" s="3" t="n">
         <v>29.9</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>7.6</v>
+        <v>76.2</v>
       </c>
       <c r="Z5" s="3" t="n">
         <v>6.8</v>
@@ -941,14 +935,14 @@
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr"/>
-      <c r="D6" s="3" t="n">
+      <c r="D6" s="8" t="n">
         <v>32.2</v>
       </c>
-      <c r="E6" s="10" t="n">
-        <v>97</v>
+      <c r="E6" s="8" t="n">
+        <v>17</v>
       </c>
       <c r="F6" s="8" t="n">
-        <v>27.6</v>
+        <v>24.6</v>
       </c>
       <c r="G6" s="3" t="n">
         <v>15.2</v>
@@ -963,49 +957,49 @@
         <v>4.4</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="L6" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="L6" s="8" t="n">
         <v>17.4</v>
       </c>
-      <c r="M6" s="11" t="n">
+      <c r="M6" s="8" t="n">
         <v>17.5</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>1.8</v>
+        <v>12.8</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>921.2</v>
+        <v>91.2</v>
       </c>
       <c r="P6" s="3" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q6" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="8" t="n">
         <v>29.5</v>
       </c>
       <c r="R6" s="3" t="n">
-        <v>24.9</v>
+        <v>24.1</v>
       </c>
       <c r="S6" s="3" t="n">
         <v>26.8</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>390.6</v>
+        <v>50.6</v>
       </c>
       <c r="U6" s="3" t="n">
-        <v>17.4</v>
-      </c>
-      <c r="V6" s="3" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="V6" s="8" t="n">
         <v>27.2</v>
       </c>
-      <c r="W6" s="11" t="n">
+      <c r="W6" s="8" t="n">
         <v>22.6</v>
       </c>
       <c r="X6" s="3" t="n">
         <v>24.2</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>27.2</v>
+        <v>37.2</v>
       </c>
       <c r="Z6" s="3" t="n">
         <v>4</v>
@@ -1024,20 +1018,20 @@
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr"/>
-      <c r="D7" s="11" t="n">
+      <c r="D7" s="8" t="n">
         <v>30.5</v>
       </c>
-      <c r="E7" s="11" t="n">
+      <c r="E7" s="8" t="n">
         <v>19.9</v>
       </c>
-      <c r="F7" s="11" t="n">
+      <c r="F7" s="8" t="n">
         <v>25.2</v>
       </c>
       <c r="G7" s="3" t="n">
         <v>10.6</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>17.9</v>
+        <v>17.8</v>
       </c>
       <c r="I7" s="3" t="n">
         <v>1.4</v>
@@ -1046,12 +1040,12 @@
         <v>2.3</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>15.2</v>
-      </c>
-      <c r="L7" s="3" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="L7" s="8" t="n">
         <v>20.3</v>
       </c>
-      <c r="M7" s="11" t="n">
+      <c r="M7" s="8" t="n">
         <v>20.2</v>
       </c>
       <c r="N7" s="3" t="n">
@@ -1063,25 +1057,25 @@
       <c r="P7" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q7" s="11" t="n">
+      <c r="Q7" s="8" t="n">
         <v>20.1</v>
       </c>
       <c r="R7" s="3" t="n">
         <v>19.5</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>2.2</v>
+        <v>22.2</v>
       </c>
       <c r="T7" s="3" t="n">
-        <v>81.2</v>
+        <v>87.2</v>
       </c>
       <c r="U7" s="3" t="n">
         <v>0.9</v>
       </c>
-      <c r="V7" s="3" t="n">
+      <c r="V7" s="8" t="n">
         <v>21.4</v>
       </c>
-      <c r="W7" s="11" t="n">
+      <c r="W7" s="8" t="n">
         <v>20.6</v>
       </c>
       <c r="X7" s="3" t="n">
@@ -1107,13 +1101,13 @@
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr"/>
-      <c r="D8" s="11" t="n">
+      <c r="D8" s="8" t="n">
         <v>26.8</v>
       </c>
-      <c r="E8" s="11" t="n">
+      <c r="E8" s="8" t="n">
         <v>18.4</v>
       </c>
-      <c r="F8" s="11" t="n">
+      <c r="F8" s="8" t="n">
         <v>22.6</v>
       </c>
       <c r="G8" s="3" t="n">
@@ -1131,20 +1125,20 @@
       <c r="K8" s="3" t="n">
         <v>1.4</v>
       </c>
-      <c r="L8" s="3" t="n">
+      <c r="L8" s="8" t="n">
         <v>18.9</v>
       </c>
-      <c r="M8" s="11" t="n">
+      <c r="M8" s="8" t="n">
         <v>18.9</v>
       </c>
       <c r="N8" s="3" t="inlineStr"/>
       <c r="O8" s="3" t="n">
-        <v>791.2</v>
+        <v>91.2</v>
       </c>
       <c r="P8" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="Q8" s="11" t="n">
+      <c r="Q8" s="8" t="n">
         <v>25.8</v>
       </c>
       <c r="R8" s="3" t="n">
@@ -1159,10 +1153,10 @@
       <c r="U8" s="3" t="n">
         <v>8.4</v>
       </c>
-      <c r="V8" s="3" t="n">
+      <c r="V8" s="8" t="n">
         <v>24.6</v>
       </c>
-      <c r="W8" s="11" t="n">
+      <c r="W8" s="8" t="n">
         <v>21.4</v>
       </c>
       <c r="X8" s="3" t="n">
@@ -1172,7 +1166,7 @@
         <v>86.2</v>
       </c>
       <c r="Z8" s="3" t="n">
-        <v>27.3</v>
+        <v>7.3</v>
       </c>
       <c r="AA8" s="3" t="inlineStr">
         <is>
@@ -1188,8 +1182,8 @@
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr"/>
-      <c r="D9" s="9" t="n">
-        <v>147.9</v>
+      <c r="D9" s="8" t="n">
+        <v>147.4</v>
       </c>
       <c r="E9" s="9" t="n">
         <v>83.59999999999999</v>
@@ -1212,17 +1206,17 @@
       <c r="K9" s="9" t="n">
         <v>44.1</v>
       </c>
-      <c r="L9" s="9" t="n">
+      <c r="L9" s="8" t="n">
         <v>92.59999999999999</v>
       </c>
-      <c r="M9" s="9" t="n">
-        <v>3972.6</v>
+      <c r="M9" s="8" t="n">
+        <v>92.59999999999999</v>
       </c>
       <c r="N9" s="3" t="n">
         <v>1</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>451.2</v>
+        <v>454.2</v>
       </c>
       <c r="P9" s="3" t="n">
         <v>0.2</v>
@@ -1242,11 +1236,11 @@
       <c r="U9" s="3" t="n">
         <v>48.8</v>
       </c>
-      <c r="V9" s="9" t="n">
+      <c r="V9" s="8" t="n">
         <v>123.8</v>
       </c>
-      <c r="W9" s="9" t="n">
-        <v>11</v>
+      <c r="W9" s="8" t="n">
+        <v>110.8</v>
       </c>
       <c r="X9" s="3" t="n">
         <v>12.6</v>
@@ -1271,46 +1265,46 @@
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr"/>
-      <c r="D10" s="11" t="n">
+      <c r="D10" s="8" t="n">
         <v>29.5</v>
       </c>
-      <c r="E10" s="11" t="n">
+      <c r="E10" s="8" t="n">
         <v>17.9</v>
       </c>
-      <c r="F10" s="11" t="n">
+      <c r="F10" s="8" t="n">
         <v>23.7</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>11.6</v>
+        <v>19.6</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="I10" s="3" t="n">
         <v>1.9</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>9.199999999999999</v>
+        <v>3.2</v>
       </c>
       <c r="K10" s="3" t="n">
         <v>0.1</v>
       </c>
-      <c r="L10" s="9" t="n">
+      <c r="L10" s="8" t="n">
         <v>18.5</v>
       </c>
-      <c r="M10" s="11" t="n">
+      <c r="M10" s="8" t="n">
         <v>18.5</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>0.2</v>
+        <v>2.8</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>291.3</v>
       </c>
       <c r="P10" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q10" s="11" t="n">
+      <c r="Q10" s="8" t="n">
         <v>25.9</v>
       </c>
       <c r="R10" s="9" t="n">
@@ -1320,25 +1314,25 @@
         <v>24.5</v>
       </c>
       <c r="T10" s="3" t="n">
-        <v>6.4</v>
+        <v>64.2</v>
       </c>
       <c r="U10" s="3" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="V10" s="9" t="n">
+      <c r="V10" s="8" t="n">
         <v>24.8</v>
       </c>
-      <c r="W10" s="11" t="n">
+      <c r="W10" s="8" t="n">
         <v>22.2</v>
       </c>
       <c r="X10" s="3" t="n">
-        <v>2.5</v>
+        <v>25.2</v>
       </c>
       <c r="Y10" s="3" t="n">
-        <v>1.6</v>
+        <v>76.2</v>
       </c>
       <c r="Z10" s="3" t="n">
-        <v>62.8</v>
+        <v>6.2</v>
       </c>
       <c r="AA10" s="3" t="inlineStr">
         <is>
@@ -1354,13 +1348,13 @@
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr"/>
-      <c r="D11" s="11" t="n">
+      <c r="D11" s="8" t="n">
         <v>29.1</v>
       </c>
-      <c r="E11" s="11" t="n">
+      <c r="E11" s="8" t="n">
         <v>18.6</v>
       </c>
-      <c r="F11" s="11" t="n">
+      <c r="F11" s="8" t="n">
         <v>23.8</v>
       </c>
       <c r="G11" s="3" t="n">
@@ -1368,15 +1362,15 @@
       </c>
       <c r="H11" s="3" t="inlineStr"/>
       <c r="I11" s="3" t="n">
-        <v>11.3</v>
+        <v>1.4</v>
       </c>
       <c r="J11" s="3" t="inlineStr"/>
       <c r="K11" s="3" t="inlineStr"/>
       <c r="L11" s="3" t="n">
         <v>8.4</v>
       </c>
-      <c r="M11" s="8" t="n">
-        <v>24.3</v>
+      <c r="M11" s="3" t="n">
+        <v>12.3</v>
       </c>
       <c r="N11" s="3" t="n">
         <v>2.8</v>
@@ -1385,13 +1379,13 @@
         <v>91.59999999999999</v>
       </c>
       <c r="P11" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="8" t="n">
         <v>28.4</v>
       </c>
       <c r="R11" s="3" t="n">
-        <v>29.8</v>
+        <v>23.8</v>
       </c>
       <c r="S11" s="3" t="n">
         <v>26.7</v>
@@ -1405,7 +1399,7 @@
       <c r="V11" s="3" t="n">
         <v>28.9</v>
       </c>
-      <c r="W11" s="11" t="n">
+      <c r="W11" s="8" t="n">
         <v>22.9</v>
       </c>
       <c r="X11" s="3" t="n">
@@ -1431,74 +1425,74 @@
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr"/>
-      <c r="D12" s="11" t="n">
+      <c r="D12" s="8" t="n">
         <v>26.5</v>
       </c>
-      <c r="E12" s="11" t="n">
+      <c r="E12" s="8" t="n">
         <v>18.4</v>
       </c>
-      <c r="F12" s="11" t="n">
+      <c r="F12" s="8" t="n">
         <v>22.4</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>984.1</v>
+        <v>28.1</v>
       </c>
       <c r="H12" s="3" t="n">
         <v>17.5</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>11.6</v>
+        <v>1.6</v>
       </c>
       <c r="J12" s="3" t="n">
         <v>2.8</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="L12" s="10" t="n">
-        <v>1.9</v>
+        <v>0.6</v>
+      </c>
+      <c r="L12" s="3" t="n">
+        <v>19</v>
       </c>
       <c r="M12" s="3" t="n">
         <v>18.8</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="O12" s="3" t="n">
         <v>90.2</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="Q12" s="10" t="n">
-        <v>2.4</v>
+        <v>0.4</v>
+      </c>
+      <c r="Q12" s="8" t="n">
+        <v>24.2</v>
       </c>
       <c r="R12" s="3" t="n">
         <v>22</v>
       </c>
       <c r="S12" s="3" t="n">
-        <v>2.5</v>
+        <v>25.1</v>
       </c>
       <c r="T12" s="3" t="n">
-        <v>61.3</v>
+        <v>67.2</v>
       </c>
       <c r="U12" s="3" t="n">
-        <v>0.5</v>
+        <v>5.2</v>
       </c>
       <c r="V12" s="3" t="n">
         <v>22.2</v>
       </c>
-      <c r="W12" s="11" t="n">
-        <v>21.9</v>
+      <c r="W12" s="8" t="n">
+        <v>21.1</v>
       </c>
       <c r="X12" s="3" t="n">
-        <v>2.4</v>
+        <v>24.4</v>
       </c>
       <c r="Y12" s="3" t="n">
         <v>81.2</v>
       </c>
       <c r="Z12" s="3" t="n">
-        <v>82.2</v>
+        <v>83.2</v>
       </c>
       <c r="AA12" s="3" t="inlineStr">
         <is>
@@ -1514,17 +1508,17 @@
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr"/>
-      <c r="D13" s="3" t="n">
+      <c r="D13" s="8" t="n">
         <v>26.8</v>
       </c>
-      <c r="E13" s="3" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="F13" s="3" t="n">
+      <c r="E13" s="8" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="F13" s="8" t="n">
         <v>22.7</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>89.3</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="H13" s="3" t="n">
         <v>17.6</v>
@@ -1533,27 +1527,27 @@
         <v>2.5</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>2.7</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="K13" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="L13" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" s="3" t="n">
         <v>19.1</v>
       </c>
       <c r="M13" s="3" t="n">
         <v>18.9</v>
       </c>
       <c r="N13" s="3" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="O13" s="3" t="n">
-        <v>9</v>
+        <v>90.2</v>
       </c>
       <c r="P13" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="Q13" s="3" t="n">
+      <c r="Q13" s="8" t="n">
         <v>22.2</v>
       </c>
       <c r="R13" s="3" t="n">
@@ -1563,25 +1557,25 @@
         <v>22.9</v>
       </c>
       <c r="T13" s="3" t="n">
-        <v>14.2</v>
+        <v>74.2</v>
       </c>
       <c r="U13" s="3" t="n">
-        <v>31.8</v>
+        <v>3.8</v>
       </c>
       <c r="V13" s="3" t="n">
         <v>21.2</v>
       </c>
-      <c r="W13" s="11" t="n">
+      <c r="W13" s="8" t="n">
         <v>20</v>
       </c>
       <c r="X13" s="3" t="n">
         <v>22.6</v>
       </c>
       <c r="Y13" s="3" t="n">
-        <v>12</v>
+        <v>2.9</v>
       </c>
       <c r="Z13" s="3" t="n">
-        <v>12.5</v>
+        <v>2.5</v>
       </c>
       <c r="AA13" s="3" t="inlineStr">
         <is>
@@ -1597,22 +1591,22 @@
         </is>
       </c>
       <c r="C14" s="3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="D14" s="11" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="D14" s="8" t="n">
         <v>29.9</v>
       </c>
-      <c r="E14" s="11" t="n">
+      <c r="E14" s="8" t="n">
         <v>18.5</v>
       </c>
-      <c r="F14" s="11" t="n">
+      <c r="F14" s="8" t="n">
         <v>24.1</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>19.5</v>
+        <v>11.5</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="I14" s="3" t="n">
         <v>1.9</v>
@@ -1621,7 +1615,7 @@
         <v>2.7</v>
       </c>
       <c r="K14" s="3" t="n">
-        <v>18.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="L14" s="3" t="n">
         <v>18.9</v>
@@ -1630,7 +1624,7 @@
         <v>18.7</v>
       </c>
       <c r="N14" s="3" t="n">
-        <v>0.2</v>
+        <v>2.8</v>
       </c>
       <c r="O14" s="3" t="n">
         <v>91.2</v>
@@ -1638,14 +1632,14 @@
       <c r="P14" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="Q14" s="3" t="n">
-        <v>31.4</v>
+      <c r="Q14" s="8" t="n">
+        <v>27.7</v>
       </c>
       <c r="R14" s="3" t="n">
         <v>23.4</v>
       </c>
       <c r="S14" s="3" t="n">
-        <v>25.8</v>
+        <v>26.2</v>
       </c>
       <c r="T14" s="3" t="n">
         <v>58.2</v>
@@ -1656,17 +1650,17 @@
       <c r="V14" s="3" t="n">
         <v>25.1</v>
       </c>
-      <c r="W14" s="11" t="n">
+      <c r="W14" s="8" t="n">
         <v>22.8</v>
       </c>
       <c r="X14" s="3" t="n">
         <v>26.4</v>
       </c>
       <c r="Y14" s="3" t="n">
-        <v>27.2</v>
+        <v>74.2</v>
       </c>
       <c r="Z14" s="3" t="n">
-        <v>51.4</v>
+        <v>5.4</v>
       </c>
       <c r="AA14" s="3" t="inlineStr">
         <is>
@@ -1682,23 +1676,23 @@
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr"/>
-      <c r="D15" s="11" t="n">
+      <c r="D15" s="8" t="n">
         <v>28.3</v>
       </c>
-      <c r="E15" s="11" t="n">
+      <c r="E15" s="8" t="n">
         <v>18.6</v>
       </c>
-      <c r="F15" s="11" t="n">
+      <c r="F15" s="8" t="n">
         <v>23.5</v>
       </c>
       <c r="G15" s="3" t="n">
         <v>9.699999999999999</v>
       </c>
-      <c r="H15" s="8" t="n">
+      <c r="H15" s="3" t="n">
         <v>17.9</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>9.6</v>
+        <v>8.6</v>
       </c>
       <c r="J15" s="3" t="n">
         <v>2.7</v>
@@ -1713,7 +1707,7 @@
         <v>18.9</v>
       </c>
       <c r="N15" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>2.8</v>
       </c>
       <c r="O15" s="3" t="n">
         <v>91.2</v>
@@ -1721,14 +1715,14 @@
       <c r="P15" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q15" s="10" t="n">
-        <v>2.6</v>
+      <c r="Q15" s="8" t="n">
+        <v>26.6</v>
       </c>
       <c r="R15" s="3" t="n">
         <v>22.9</v>
       </c>
       <c r="S15" s="3" t="n">
-        <v>20.7</v>
+        <v>10.7</v>
       </c>
       <c r="T15" s="3" t="n">
         <v>58.2</v>
@@ -1737,19 +1731,19 @@
         <v>9.1</v>
       </c>
       <c r="V15" s="3" t="n">
-        <v>28.4</v>
-      </c>
-      <c r="W15" s="11" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="W15" s="8" t="n">
         <v>20.9</v>
       </c>
       <c r="X15" s="3" t="n">
         <v>24.4</v>
       </c>
       <c r="Y15" s="3" t="n">
-        <v>8.5</v>
+        <v>85.3</v>
       </c>
       <c r="Z15" s="3" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="AA15" s="3" t="inlineStr">
         <is>
@@ -1765,11 +1759,11 @@
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr"/>
-      <c r="D16" s="9" t="n">
-        <v>14</v>
+      <c r="D16" s="8" t="n">
+        <v>140.4</v>
       </c>
       <c r="E16" s="9" t="n">
-        <v>112.3</v>
+        <v>12.3</v>
       </c>
       <c r="F16" s="9" t="n">
         <v>116.6</v>
@@ -1781,12 +1775,12 @@
         <v>81.5</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>29.3</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>14.3</v>
-      </c>
-      <c r="K16" s="12" t="inlineStr"/>
+        <v>17.3</v>
+      </c>
+      <c r="K16" s="11" t="inlineStr"/>
       <c r="L16" s="9" t="n">
         <v>95.3</v>
       </c>
@@ -1797,16 +1791,16 @@
         <v>1</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>853.2</v>
+        <v>153.2</v>
       </c>
       <c r="P16" s="3" t="n">
         <v>1.4</v>
       </c>
-      <c r="Q16" s="9" t="n">
-        <v>127.2</v>
+      <c r="Q16" s="8" t="n">
+        <v>129.2</v>
       </c>
       <c r="R16" s="9" t="n">
-        <v>122.3</v>
+        <v>182.5</v>
       </c>
       <c r="S16" s="3" t="n">
         <v>126.6</v>
@@ -1815,19 +1809,19 @@
         <v>38.2</v>
       </c>
       <c r="U16" s="3" t="n">
-        <v>99.2</v>
+        <v>41.2</v>
       </c>
       <c r="V16" s="9" t="n">
-        <v>187.8</v>
+        <v>116.7</v>
       </c>
       <c r="W16" s="9" t="n">
-        <v>10.8</v>
+        <v>10.1</v>
       </c>
       <c r="X16" s="3" t="n">
         <v>124.6</v>
       </c>
       <c r="Y16" s="3" t="n">
-        <v>970.8</v>
+        <v>408.9</v>
       </c>
       <c r="Z16" s="3" t="n">
         <v>15</v>
@@ -1845,18 +1839,20 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C17" s="3" t="inlineStr"/>
-      <c r="D17" s="9" t="n">
-        <v>28.4</v>
-      </c>
-      <c r="E17" s="9" t="n">
-        <v>18.3</v>
-      </c>
-      <c r="F17" s="10" t="n">
-        <v>1.3</v>
+      <c r="C17" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D17" s="8" t="n">
+        <v>28.1</v>
+      </c>
+      <c r="E17" s="8" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="F17" s="8" t="n">
+        <v>23.3</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>9.1</v>
+        <v>9.6</v>
       </c>
       <c r="H17" s="3" t="n">
         <v>12.5</v>
@@ -1865,47 +1861,47 @@
         <v>1.9</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>22.9</v>
+        <v>2.9</v>
       </c>
       <c r="K17" s="3" t="inlineStr"/>
       <c r="L17" s="9" t="n">
-        <v>19.9</v>
+        <v>19.1</v>
       </c>
       <c r="M17" s="9" t="n">
-        <v>18.5</v>
+        <v>18.9</v>
       </c>
       <c r="N17" s="3" t="n">
-        <v>2.1</v>
+        <v>22.1</v>
       </c>
       <c r="O17" s="3" t="n">
-        <v>21.2</v>
+        <v>91.2</v>
       </c>
       <c r="P17" s="3" t="n">
         <v>0.3</v>
       </c>
-      <c r="Q17" s="9" t="n">
+      <c r="Q17" s="8" t="n">
         <v>25.8</v>
       </c>
       <c r="R17" s="9" t="n">
-        <v>22.5</v>
+        <v>12.5</v>
       </c>
       <c r="S17" s="3" t="n">
         <v>25.3</v>
       </c>
       <c r="T17" s="3" t="n">
-        <v>6.4</v>
+        <v>64.2</v>
       </c>
       <c r="U17" s="3" t="n">
-        <v>82.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="V17" s="9" t="n">
         <v>22.9</v>
       </c>
-      <c r="W17" s="11" t="n">
+      <c r="W17" s="8" t="n">
         <v>21.5</v>
       </c>
       <c r="X17" s="3" t="n">
-        <v>24.8</v>
+        <v>24.9</v>
       </c>
       <c r="Y17" s="3" t="n">
         <v>82.2</v>
@@ -1940,7 +1936,7 @@
         <v>12.4</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>12.6</v>
+        <v>16.6</v>
       </c>
       <c r="I18" s="3" t="n">
         <v>2.1</v>
@@ -1948,28 +1944,28 @@
       <c r="J18" s="3" t="n">
         <v>3.6</v>
       </c>
-      <c r="K18" s="3" t="n">
+      <c r="K18" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="L18" s="3" t="n">
+      <c r="L18" s="8" t="n">
         <v>19.2</v>
       </c>
-      <c r="M18" s="10" t="n">
-        <v>1.3</v>
+      <c r="M18" s="8" t="n">
+        <v>19.6</v>
       </c>
       <c r="N18" s="3" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="O18" s="3" t="n">
-        <v>291.2</v>
+        <v>91.2</v>
       </c>
       <c r="P18" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q18" s="10" t="n">
+      <c r="Q18" s="13" t="n">
         <v>89.2</v>
       </c>
-      <c r="R18" s="3" t="n">
+      <c r="R18" s="8" t="n">
         <v>23.2</v>
       </c>
       <c r="S18" s="3" t="n">
@@ -1979,10 +1975,10 @@
         <v>54.2</v>
       </c>
       <c r="U18" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="V18" s="3" t="n">
-        <v>21.8</v>
+        <v>10.1</v>
+      </c>
+      <c r="V18" s="13" t="n">
+        <v>12.18</v>
       </c>
       <c r="W18" s="3" t="n">
         <v>20.8</v>
@@ -2010,22 +2006,22 @@
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="D19" s="11" t="n">
-        <v>30.3</v>
-      </c>
-      <c r="E19" s="11" t="n">
-        <v>17.6</v>
-      </c>
-      <c r="F19" s="11" t="n">
-        <v>24</v>
+        <v>0.1</v>
+      </c>
+      <c r="D19" s="8" t="n">
+        <v>30.6</v>
+      </c>
+      <c r="E19" s="8" t="n">
+        <v>17.7</v>
+      </c>
+      <c r="F19" s="8" t="n">
+        <v>24.1</v>
       </c>
       <c r="G19" s="3" t="n">
         <v>12.9</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>15.4</v>
+        <v>16.4</v>
       </c>
       <c r="I19" s="3" t="n">
         <v>1.5</v>
@@ -2033,17 +2029,17 @@
       <c r="J19" s="3" t="n">
         <v>2.5</v>
       </c>
-      <c r="K19" s="3" t="n">
+      <c r="K19" s="8" t="n">
         <v>27.9</v>
       </c>
-      <c r="L19" s="3" t="n">
+      <c r="L19" s="8" t="n">
         <v>18.3</v>
       </c>
-      <c r="M19" s="3" t="n">
-        <v>18.6</v>
+      <c r="M19" s="8" t="n">
+        <v>18.2</v>
       </c>
       <c r="N19" s="3" t="n">
-        <v>0.9</v>
+        <v>0.1</v>
       </c>
       <c r="O19" s="3" t="n">
         <v>92.2</v>
@@ -2054,29 +2050,29 @@
       <c r="Q19" s="3" t="n">
         <v>19.9</v>
       </c>
-      <c r="R19" s="3" t="n">
+      <c r="R19" s="8" t="n">
         <v>19.8</v>
       </c>
       <c r="S19" s="3" t="n">
         <v>23</v>
       </c>
       <c r="T19" s="3" t="n">
-        <v>20.2</v>
+        <v>90.2</v>
       </c>
       <c r="U19" s="3" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="V19" s="3" t="n">
         <v>20.2</v>
       </c>
       <c r="W19" s="3" t="n">
-        <v>12.9</v>
+        <v>19.9</v>
       </c>
       <c r="X19" s="3" t="n">
         <v>23</v>
       </c>
       <c r="Y19" s="3" t="n">
-        <v>81.8</v>
+        <v>81.2</v>
       </c>
       <c r="Z19" s="3" t="n">
         <v>0.6</v>
@@ -2095,19 +2091,19 @@
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="D20" s="11" t="n">
-        <v>28.6</v>
-      </c>
-      <c r="E20" s="11" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="F20" s="11" t="n">
-        <v>23.6</v>
-      </c>
-      <c r="G20" s="8" t="n">
-        <v>59.6</v>
+        <v>0.1</v>
+      </c>
+      <c r="D20" s="8" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="E20" s="8" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="F20" s="8" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="G20" s="3" t="n">
+        <v>29.6</v>
       </c>
       <c r="H20" s="3" t="n">
         <v>17.6</v>
@@ -2116,16 +2112,16 @@
         <v>1.2</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="K20" s="3" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="K20" s="8" t="n">
         <v>0</v>
       </c>
       <c r="L20" s="8" t="n">
-        <v>19.8</v>
-      </c>
-      <c r="M20" s="3" t="n">
-        <v>18.2</v>
+        <v>19.2</v>
+      </c>
+      <c r="M20" s="8" t="n">
+        <v>19.2</v>
       </c>
       <c r="N20" s="3" t="inlineStr"/>
       <c r="O20" s="3" t="n">
@@ -2134,20 +2130,20 @@
       <c r="P20" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="Q20" s="10" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="R20" s="3" t="n">
+      <c r="Q20" s="3" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="R20" s="8" t="n">
         <v>21.9</v>
       </c>
       <c r="S20" s="3" t="n">
-        <v>20.7</v>
+        <v>29.7</v>
       </c>
       <c r="T20" s="3" t="n">
-        <v>22.2</v>
+        <v>72.2</v>
       </c>
       <c r="U20" s="3" t="n">
-        <v>10.3</v>
+        <v>10.9</v>
       </c>
       <c r="V20" s="3" t="n">
         <v>22.8</v>
@@ -2155,8 +2151,8 @@
       <c r="W20" s="3" t="n">
         <v>20.2</v>
       </c>
-      <c r="X20" s="8" t="n">
-        <v>23.2</v>
+      <c r="X20" s="3" t="n">
+        <v>25.3</v>
       </c>
       <c r="Y20" s="3" t="n">
         <v>2.6</v>
@@ -2180,13 +2176,13 @@
       <c r="C21" s="3" t="n">
         <v>1.1</v>
       </c>
-      <c r="D21" s="11" t="n">
+      <c r="D21" s="8" t="n">
         <v>28.4</v>
       </c>
-      <c r="E21" s="11" t="n">
+      <c r="E21" s="8" t="n">
         <v>18.4</v>
       </c>
-      <c r="F21" s="11" t="n">
+      <c r="F21" s="8" t="n">
         <v>23.4</v>
       </c>
       <c r="G21" s="3" t="n">
@@ -2201,16 +2197,18 @@
       <c r="J21" s="3" t="n">
         <v>1.9</v>
       </c>
-      <c r="K21" s="3" t="n">
+      <c r="K21" s="8" t="n">
         <v>3.8</v>
       </c>
-      <c r="L21" s="3" t="n">
+      <c r="L21" s="8" t="n">
         <v>19.4</v>
       </c>
-      <c r="M21" s="3" t="n">
+      <c r="M21" s="8" t="n">
         <v>18.4</v>
       </c>
-      <c r="N21" s="3" t="inlineStr"/>
+      <c r="N21" s="3" t="n">
+        <v>0.1</v>
+      </c>
       <c r="O21" s="3" t="n">
         <v>92.2</v>
       </c>
@@ -2220,20 +2218,20 @@
       <c r="Q21" s="3" t="n">
         <v>19.2</v>
       </c>
-      <c r="R21" s="10" t="n">
-        <v>1.3</v>
+      <c r="R21" s="8" t="n">
+        <v>19.1</v>
       </c>
       <c r="S21" s="3" t="n">
         <v>22</v>
       </c>
       <c r="T21" s="3" t="n">
-        <v>88.7</v>
+        <v>28.2</v>
       </c>
       <c r="U21" s="3" t="n">
-        <v>0.8</v>
+        <v>0.2</v>
       </c>
       <c r="V21" s="3" t="n">
-        <v>12.5</v>
+        <v>19.5</v>
       </c>
       <c r="W21" s="3" t="n">
         <v>19.1</v>
@@ -2242,7 +2240,7 @@
         <v>21.9</v>
       </c>
       <c r="Y21" s="3" t="n">
-        <v>90.3</v>
+        <v>90.2</v>
       </c>
       <c r="Z21" s="3" t="n">
         <v>0.8</v>
@@ -2261,64 +2259,64 @@
         </is>
       </c>
       <c r="C22" s="3" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="D22" s="11" t="n">
-        <v>29.4</v>
-      </c>
-      <c r="E22" s="11" t="n">
-        <v>17.8</v>
-      </c>
-      <c r="F22" s="11" t="n">
-        <v>23.6</v>
+        <v>0.1</v>
+      </c>
+      <c r="D22" s="8" t="n">
+        <v>29.2</v>
+      </c>
+      <c r="E22" s="8" t="n">
+        <v>17</v>
+      </c>
+      <c r="F22" s="8" t="n">
+        <v>23.3</v>
       </c>
       <c r="G22" s="3" t="n">
         <v>12.2</v>
       </c>
       <c r="H22" s="3" t="n">
-        <v>1.5</v>
+        <v>15.9</v>
       </c>
       <c r="I22" s="3" t="n">
-        <v>11.8</v>
+        <v>1.8</v>
       </c>
       <c r="J22" s="3" t="n">
         <v>3.2</v>
       </c>
-      <c r="K22" s="3" t="n">
+      <c r="K22" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="L22" s="10" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="M22" s="3" t="n">
+      <c r="L22" s="8" t="n">
         <v>18</v>
       </c>
+      <c r="M22" s="8" t="n">
+        <v>18</v>
+      </c>
       <c r="N22" s="3" t="n">
-        <v>0.1</v>
+        <v>8.1</v>
       </c>
       <c r="O22" s="3" t="n">
-        <v>991.2</v>
+        <v>91.2</v>
       </c>
       <c r="P22" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="Q22" s="10" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="R22" s="10" t="n">
-        <v>2.2</v>
+      <c r="Q22" s="3" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="R22" s="8" t="n">
+        <v>23.1</v>
       </c>
       <c r="S22" s="3" t="n">
         <v>25</v>
       </c>
       <c r="T22" s="3" t="n">
-        <v>86.2</v>
+        <v>56.2</v>
       </c>
       <c r="U22" s="3" t="n">
-        <v>13.9</v>
-      </c>
-      <c r="V22" s="10" t="n">
-        <v>2.4</v>
+        <v>19.9</v>
+      </c>
+      <c r="V22" s="3" t="n">
+        <v>24.6</v>
       </c>
       <c r="W22" s="3" t="n">
         <v>26.2</v>
@@ -2347,10 +2345,10 @@
       </c>
       <c r="C23" s="3" t="inlineStr"/>
       <c r="D23" s="9" t="n">
-        <v>1942.6</v>
+        <v>147.6</v>
       </c>
       <c r="E23" s="9" t="n">
-        <v>10.4</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="F23" s="9" t="n">
         <v>112.2</v>
@@ -2359,44 +2357,44 @@
         <v>52.2</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>23.8</v>
+        <v>83.8</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>12.6</v>
+        <v>7.6</v>
       </c>
       <c r="J23" s="3" t="n">
         <v>14</v>
       </c>
-      <c r="K23" s="9" t="n">
-        <v>28.7</v>
+      <c r="K23" s="8" t="n">
+        <v>31.7</v>
       </c>
       <c r="L23" s="9" t="n">
-        <v>93.90000000000001</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="M23" s="9" t="n">
-        <v>1952.9</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>0.8</v>
+        <v>8.1</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>951.2</v>
+        <v>451.2</v>
       </c>
       <c r="P23" s="3" t="inlineStr"/>
       <c r="Q23" s="9" t="n">
         <v>121</v>
       </c>
-      <c r="R23" s="9" t="n">
+      <c r="R23" s="8" t="n">
         <v>107.2</v>
       </c>
       <c r="S23" s="3" t="n">
-        <v>11.9</v>
+        <v>119.7</v>
       </c>
       <c r="T23" s="3" t="n">
-        <v>36</v>
+        <v>360.2</v>
       </c>
       <c r="U23" s="3" t="n">
-        <v>37.7</v>
+        <v>34.7</v>
       </c>
       <c r="V23" s="9" t="n">
         <v>108.4</v>
@@ -2405,10 +2403,10 @@
         <v>102.6</v>
       </c>
       <c r="X23" s="3" t="n">
-        <v>198.7</v>
+        <v>117.8</v>
       </c>
       <c r="Y23" s="3" t="n">
-        <v>9425.6</v>
+        <v>427.6</v>
       </c>
       <c r="Z23" s="3" t="n">
         <v>12.7</v>
@@ -2427,7 +2425,7 @@
         </is>
       </c>
       <c r="C24" s="3" t="n">
-        <v>1.1</v>
+        <v>0.1</v>
       </c>
       <c r="D24" s="9" t="n">
         <v>28.5</v>
@@ -2450,20 +2448,20 @@
       <c r="J24" s="3" t="n">
         <v>1.8</v>
       </c>
-      <c r="K24" s="8" t="n">
-        <v>65.59999999999999</v>
-      </c>
-      <c r="L24" s="9" t="n">
-        <v>98.8</v>
-      </c>
-      <c r="M24" s="9" t="n">
+      <c r="K24" s="3" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="L24" s="8" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="M24" s="8" t="n">
         <v>18.6</v>
       </c>
       <c r="N24" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="O24" s="3" t="n">
-        <v>91.2</v>
+        <v>31.2</v>
       </c>
       <c r="P24" s="3" t="n">
         <v>0.2</v>
@@ -2471,14 +2469,14 @@
       <c r="Q24" s="9" t="n">
         <v>27.2</v>
       </c>
-      <c r="R24" s="9" t="n">
-        <v>21.6</v>
+      <c r="R24" s="8" t="n">
+        <v>21.4</v>
       </c>
       <c r="S24" s="3" t="n">
         <v>23.9</v>
       </c>
       <c r="T24" s="3" t="n">
-        <v>72.3</v>
+        <v>72.2</v>
       </c>
       <c r="U24" s="3" t="n">
         <v>6.9</v>
@@ -2496,7 +2494,7 @@
         <v>2.5</v>
       </c>
       <c r="Z24" s="3" t="n">
-        <v>85.8</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="AA24" s="3" t="inlineStr">
         <is>
@@ -2512,23 +2510,23 @@
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr"/>
-      <c r="D25" s="11" t="n">
-        <v>29.9</v>
-      </c>
-      <c r="E25" s="11" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="F25" s="11" t="n">
+      <c r="D25" s="8" t="n">
+        <v>29.8</v>
+      </c>
+      <c r="E25" s="8" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="F25" s="8" t="n">
         <v>24.2</v>
       </c>
       <c r="G25" s="3" t="n">
         <v>444.1</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>17.9</v>
+        <v>17.1</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="J25" s="3" t="n">
         <v>34.4</v>
@@ -2537,46 +2535,46 @@
         <v>0</v>
       </c>
       <c r="L25" s="3" t="n">
-        <v>12.9</v>
-      </c>
-      <c r="M25" s="8" t="n">
-        <v>12.9</v>
+        <v>19.1</v>
+      </c>
+      <c r="M25" s="3" t="n">
+        <v>19.1</v>
       </c>
       <c r="N25" s="3" t="n">
         <v>0.1</v>
       </c>
       <c r="O25" s="3" t="n">
-        <v>59.2</v>
+        <v>92.2</v>
       </c>
       <c r="P25" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="Q25" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="13" t="n">
         <v>2.6</v>
       </c>
-      <c r="R25" s="10" t="n">
+      <c r="R25" s="13" t="n">
         <v>3</v>
       </c>
       <c r="S25" s="3" t="n">
         <v>26.4</v>
       </c>
       <c r="T25" s="3" t="n">
-        <v>31.2</v>
+        <v>71.2</v>
       </c>
       <c r="U25" s="3" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="V25" s="11" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="V25" s="3" t="n">
         <v>25.3</v>
       </c>
-      <c r="W25" s="10" t="n">
+      <c r="W25" s="13" t="n">
         <v>4.9</v>
       </c>
       <c r="X25" s="3" t="n">
-        <v>23.9</v>
+        <v>23.1</v>
       </c>
       <c r="Y25" s="3" t="n">
-        <v>69.3</v>
+        <v>67.2</v>
       </c>
       <c r="Z25" s="3" t="inlineStr"/>
       <c r="AA25" s="3" t="inlineStr">
@@ -2593,25 +2591,25 @@
         </is>
       </c>
       <c r="C26" s="3" t="n">
-        <v>111.6</v>
-      </c>
-      <c r="D26" s="11" t="n">
-        <v>32.6</v>
-      </c>
-      <c r="E26" s="11" t="n">
-        <v>15.2</v>
-      </c>
-      <c r="F26" s="11" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="D26" s="8" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="E26" s="8" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="F26" s="8" t="n">
         <v>23.9</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>9.4</v>
+        <v>18.4</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>1.6</v>
+        <v>16.7</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>1.2</v>
+        <v>0.2</v>
       </c>
       <c r="J26" s="3" t="n">
         <v>1.9</v>
@@ -2622,14 +2620,14 @@
       <c r="L26" s="3" t="n">
         <v>19.6</v>
       </c>
-      <c r="M26" s="10" t="n">
-        <v>98.96000000000001</v>
+      <c r="M26" s="3" t="n">
+        <v>29.6</v>
       </c>
       <c r="N26" s="3" t="n">
         <v>1.8</v>
       </c>
       <c r="O26" s="3" t="n">
-        <v>8.1</v>
+        <v>91.2</v>
       </c>
       <c r="P26" s="3" t="n">
         <v>0</v>
@@ -2638,10 +2636,10 @@
         <v>25.8</v>
       </c>
       <c r="R26" s="3" t="n">
-        <v>23.3</v>
+        <v>29.3</v>
       </c>
       <c r="S26" s="3" t="n">
-        <v>17.9</v>
+        <v>27.1</v>
       </c>
       <c r="T26" s="3" t="n">
         <v>76.2</v>
@@ -2649,7 +2647,7 @@
       <c r="U26" s="3" t="n">
         <v>5.9</v>
       </c>
-      <c r="V26" s="11" t="n">
+      <c r="V26" s="3" t="n">
         <v>20.9</v>
       </c>
       <c r="W26" s="3" t="n">
@@ -2678,47 +2676,47 @@
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr"/>
-      <c r="D27" s="11" t="n">
-        <v>27.4</v>
-      </c>
-      <c r="E27" s="11" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="F27" s="11" t="n">
+      <c r="D27" s="8" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="E27" s="8" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="F27" s="8" t="n">
         <v>22.4</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>9.800000000000001</v>
+        <v>9.9</v>
       </c>
       <c r="H27" s="3" t="n">
         <v>15.8</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>19.8</v>
+        <v>1.9</v>
       </c>
       <c r="J27" s="3" t="n">
         <v>3</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>6.2</v>
+        <v>2.1</v>
       </c>
       <c r="L27" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="M27" s="10" t="n">
-        <v>1.8</v>
+      <c r="M27" s="3" t="n">
+        <v>18</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>1.8</v>
+        <v>18.2</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>922.2</v>
+        <v>98.2</v>
       </c>
       <c r="P27" s="3" t="n">
         <v>0</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>26.6</v>
+        <v>20.6</v>
       </c>
       <c r="R27" s="3" t="n">
         <v>22.1</v>
@@ -2727,12 +2725,12 @@
         <v>23.9</v>
       </c>
       <c r="T27" s="3" t="n">
-        <v>63.2</v>
+        <v>0.1</v>
       </c>
       <c r="U27" s="3" t="n">
         <v>10.9</v>
       </c>
-      <c r="V27" s="11" t="n">
+      <c r="V27" s="3" t="n">
         <v>23.9</v>
       </c>
       <c r="W27" s="3" t="n">
@@ -2761,17 +2759,17 @@
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr"/>
-      <c r="D28" s="11" t="n">
-        <v>30.7</v>
-      </c>
-      <c r="E28" s="11" t="n">
-        <v>17.9</v>
-      </c>
-      <c r="F28" s="11" t="n">
+      <c r="D28" s="8" t="n">
+        <v>32.7</v>
+      </c>
+      <c r="E28" s="8" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="F28" s="8" t="n">
         <v>24.3</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>15.8</v>
+        <v>16.8</v>
       </c>
       <c r="H28" s="3" t="n">
         <v>14</v>
@@ -2785,23 +2783,23 @@
       <c r="K28" s="3" t="n">
         <v>0.3</v>
       </c>
-      <c r="L28" s="10" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="M28" s="10" t="n">
-        <v>1.6</v>
+      <c r="L28" s="3" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="M28" s="3" t="n">
+        <v>16.2</v>
       </c>
       <c r="N28" s="3" t="n">
-        <v>14.8</v>
+        <v>18.8</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>92.2</v>
+        <v>92.8</v>
       </c>
       <c r="P28" s="3" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="Q28" s="3" t="n">
-        <v>20.9</v>
+        <v>30.1</v>
       </c>
       <c r="R28" s="3" t="n">
         <v>23.3</v>
@@ -2810,19 +2808,19 @@
         <v>24.5</v>
       </c>
       <c r="T28" s="3" t="n">
-        <v>4</v>
+        <v>40.2</v>
       </c>
       <c r="U28" s="3" t="n">
-        <v>18.2</v>
-      </c>
-      <c r="V28" s="11" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="V28" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="W28" s="10" t="n">
-        <v>2.1</v>
+      <c r="W28" s="3" t="n">
+        <v>27.8</v>
       </c>
       <c r="X28" s="3" t="n">
-        <v>21.2</v>
+        <v>216.2</v>
       </c>
       <c r="Y28" s="3" t="n">
         <v>14.6</v>
@@ -2844,14 +2842,14 @@
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr"/>
-      <c r="D29" s="11" t="n">
-        <v>30.2</v>
-      </c>
-      <c r="E29" s="11" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="F29" s="11" t="n">
-        <v>24.2</v>
+      <c r="D29" s="8" t="n">
+        <v>30.1</v>
+      </c>
+      <c r="E29" s="8" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="F29" s="8" t="n">
+        <v>24.3</v>
       </c>
       <c r="G29" s="3" t="n">
         <v>19.7</v>
@@ -2869,14 +2867,14 @@
         <v>0.5</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>19.2</v>
-      </c>
-      <c r="M29" s="13" t="inlineStr"/>
+        <v>18.2</v>
+      </c>
+      <c r="M29" s="12" t="inlineStr"/>
       <c r="N29" s="3" t="n">
-        <v>0.1</v>
+        <v>9.6</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>90.2</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="P29" s="3" t="n">
         <v>0</v>
@@ -2891,13 +2889,13 @@
         <v>14.5</v>
       </c>
       <c r="T29" s="3" t="n">
-        <v>12.2</v>
+        <v>72.2</v>
       </c>
       <c r="U29" s="3" t="n">
         <v>2.5</v>
       </c>
-      <c r="V29" s="11" t="n">
-        <v>13.4</v>
+      <c r="V29" s="3" t="n">
+        <v>19.4</v>
       </c>
       <c r="W29" s="3" t="n">
         <v>21.8</v>
@@ -2909,7 +2907,7 @@
         <v>2.3</v>
       </c>
       <c r="Z29" s="3" t="n">
-        <v>20.1</v>
+        <v>20.6</v>
       </c>
       <c r="AA29" s="3" t="inlineStr">
         <is>
@@ -2925,23 +2923,23 @@
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr"/>
-      <c r="D30" s="9" t="n">
-        <v>1498.4</v>
-      </c>
-      <c r="E30" s="9" t="n">
-        <v>189.6</v>
-      </c>
-      <c r="F30" s="9" t="n">
-        <v>11.8</v>
+      <c r="D30" s="8" t="n">
+        <v>148.4</v>
+      </c>
+      <c r="E30" s="8" t="n">
+        <v>89.59999999999999</v>
+      </c>
+      <c r="F30" s="8" t="n">
+        <v>119.1</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>5.8</v>
+        <v>58.8</v>
       </c>
       <c r="H30" s="3" t="n">
         <v>80.59999999999999</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>10.9</v>
+        <v>10.5</v>
       </c>
       <c r="J30" s="3" t="n">
         <v>17.8</v>
@@ -2950,10 +2948,10 @@
         <v>8.300000000000001</v>
       </c>
       <c r="L30" s="9" t="n">
-        <v>292.5</v>
+        <v>92.5</v>
       </c>
       <c r="M30" s="9" t="n">
-        <v>392.1</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="N30" s="3" t="inlineStr"/>
       <c r="O30" s="3" t="n">
@@ -2978,16 +2976,16 @@
         <v>118.2</v>
       </c>
       <c r="V30" s="9" t="n">
-        <v>104.1</v>
+        <v>104.6</v>
       </c>
       <c r="W30" s="9" t="n">
         <v>114.6</v>
       </c>
       <c r="X30" s="3" t="n">
-        <v>312.2</v>
+        <v>372.2</v>
       </c>
       <c r="Y30" s="3" t="n">
-        <v>52.4</v>
+        <v>32.4</v>
       </c>
       <c r="Z30" s="3" t="n">
         <v>33</v>
@@ -3006,36 +3004,36 @@
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr"/>
-      <c r="D31" s="11" t="n">
-        <v>29.9</v>
-      </c>
-      <c r="E31" s="11" t="n">
-        <v>17.9</v>
-      </c>
-      <c r="F31" s="11" t="n">
-        <v>23.8</v>
+      <c r="D31" s="9" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="E31" s="9" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="F31" s="9" t="n">
+        <v>22.9</v>
       </c>
       <c r="G31" s="3" t="n">
         <v>19.8</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>18.1</v>
+        <v>16.1</v>
       </c>
       <c r="I31" s="3" t="n">
         <v>2.1</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>1.6</v>
+        <v>2.6</v>
       </c>
       <c r="K31" s="3" t="inlineStr"/>
       <c r="L31" s="9" t="n">
-        <v>10.3</v>
+        <v>18.9</v>
       </c>
       <c r="M31" s="9" t="n">
         <v>18.5</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>28.4</v>
+        <v>24</v>
       </c>
       <c r="O31" s="3" t="n">
         <v>91.2</v>
@@ -3044,7 +3042,7 @@
         <v>0</v>
       </c>
       <c r="Q31" s="9" t="n">
-        <v>26.9</v>
+        <v>26.1</v>
       </c>
       <c r="R31" s="9" t="n">
         <v>22.6</v>
@@ -3058,14 +3056,14 @@
       <c r="U31" s="3" t="n">
         <v>8.9</v>
       </c>
-      <c r="V31" s="11" t="n">
+      <c r="V31" s="9" t="n">
         <v>20.8</v>
       </c>
       <c r="W31" s="9" t="n">
-        <v>22.7</v>
-      </c>
-      <c r="X31" s="8" t="n">
-        <v>47.8</v>
+        <v>22.9</v>
+      </c>
+      <c r="X31" s="3" t="n">
+        <v>77.8</v>
       </c>
       <c r="Y31" s="3" t="n">
         <v>6.5</v>
@@ -3089,17 +3087,17 @@
       <c r="C32" s="3" t="n">
         <v>1.1</v>
       </c>
-      <c r="D32" s="10" t="n">
-        <v>23.28</v>
-      </c>
-      <c r="E32" s="10" t="n">
+      <c r="D32" s="8" t="n">
+        <v>32.8</v>
+      </c>
+      <c r="E32" s="13" t="n">
         <v>4.5</v>
       </c>
-      <c r="F32" s="10" t="n">
+      <c r="F32" s="13" t="n">
         <v>35</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>17.5</v>
+        <v>14.5</v>
       </c>
       <c r="H32" s="3" t="n">
         <v>17.5</v>
@@ -3108,50 +3106,50 @@
         <v>9.4</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="K32" s="3" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="K32" s="8" t="n">
         <v>22.5</v>
       </c>
-      <c r="L32" s="13" t="inlineStr"/>
+      <c r="L32" s="12" t="inlineStr"/>
       <c r="M32" s="3" t="n">
-        <v>18.1</v>
+        <v>18.7</v>
       </c>
       <c r="N32" s="3" t="n">
-        <v>8.699999999999999</v>
+        <v>87.59999999999999</v>
       </c>
       <c r="O32" s="3" t="n">
-        <v>99.59999999999999</v>
+        <v>91.2</v>
       </c>
       <c r="P32" s="3" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="Q32" s="3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Q32" s="8" t="n">
         <v>29.9</v>
       </c>
-      <c r="R32" s="3" t="n">
+      <c r="R32" s="8" t="n">
         <v>24</v>
       </c>
       <c r="S32" s="3" t="n">
         <v>26.8</v>
       </c>
       <c r="T32" s="3" t="n">
-        <v>3.5</v>
+        <v>35.8</v>
       </c>
       <c r="U32" s="3" t="n">
         <v>15.5</v>
       </c>
-      <c r="V32" s="10" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="W32" s="11" t="n">
+      <c r="V32" s="8" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="W32" s="8" t="n">
         <v>25.8</v>
       </c>
       <c r="X32" s="3" t="n">
         <v>85.3</v>
       </c>
       <c r="Y32" s="3" t="n">
-        <v>22.4</v>
+        <v>23.4</v>
       </c>
       <c r="Z32" s="3" t="inlineStr"/>
       <c r="AA32" s="3" t="inlineStr">
@@ -3168,19 +3166,19 @@
         </is>
       </c>
       <c r="C33" s="3" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="D33" s="10" t="n">
-        <v>92.59999999999999</v>
-      </c>
-      <c r="E33" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D33" s="8" t="n">
+        <v>32.6</v>
+      </c>
+      <c r="E33" s="8" t="n">
         <v>18</v>
       </c>
-      <c r="F33" s="10" t="n">
-        <v>2.5</v>
+      <c r="F33" s="8" t="n">
+        <v>25.3</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>1.4</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="H33" s="3" t="n">
         <v>17.9</v>
@@ -3191,48 +3189,48 @@
       <c r="J33" s="3" t="n">
         <v>4.5</v>
       </c>
-      <c r="K33" s="3" t="n">
+      <c r="K33" s="8" t="n">
         <v>0</v>
       </c>
       <c r="L33" s="3" t="n">
-        <v>19.8</v>
-      </c>
-      <c r="M33" s="10" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="M33" s="13" t="n">
         <v>1.8</v>
       </c>
       <c r="N33" s="3" t="inlineStr"/>
       <c r="O33" s="3" t="n">
-        <v>8</v>
+        <v>90.3</v>
       </c>
       <c r="P33" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="Q33" s="3" t="n">
+      <c r="Q33" s="8" t="n">
         <v>28.9</v>
       </c>
-      <c r="R33" s="3" t="n">
+      <c r="R33" s="8" t="n">
         <v>24.8</v>
       </c>
       <c r="S33" s="3" t="n">
         <v>28.8</v>
       </c>
       <c r="T33" s="3" t="n">
-        <v>7.8</v>
+        <v>48.2</v>
       </c>
       <c r="U33" s="3" t="n">
-        <v>24.2</v>
-      </c>
-      <c r="V33" s="3" t="n">
-        <v>29</v>
-      </c>
-      <c r="W33" s="11" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="V33" s="8" t="n">
+        <v>22</v>
+      </c>
+      <c r="W33" s="8" t="n">
         <v>27.4</v>
       </c>
       <c r="X33" s="3" t="n">
         <v>80.3</v>
       </c>
       <c r="Y33" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>2.8</v>
       </c>
       <c r="Z33" s="3" t="n">
         <v>15</v>
@@ -3250,20 +3248,22 @@
           <t>23</t>
         </is>
       </c>
-      <c r="C34" s="3" t="inlineStr"/>
-      <c r="D34" s="3" t="n">
-        <v>32.1</v>
-      </c>
-      <c r="E34" s="3" t="n">
-        <v>19.4</v>
-      </c>
-      <c r="F34" s="3" t="n">
-        <v>26.8</v>
+      <c r="C34" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D34" s="8" t="n">
+        <v>32.2</v>
+      </c>
+      <c r="E34" s="8" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="F34" s="8" t="n">
+        <v>25.8</v>
       </c>
       <c r="G34" s="3" t="n">
         <v>12.7</v>
       </c>
-      <c r="H34" s="8" t="n">
+      <c r="H34" s="3" t="n">
         <v>18</v>
       </c>
       <c r="I34" s="3" t="n">
@@ -3272,50 +3272,50 @@
       <c r="J34" s="3" t="n">
         <v>3.5</v>
       </c>
-      <c r="K34" s="3" t="n">
+      <c r="K34" s="8" t="n">
         <v>13.5</v>
       </c>
       <c r="L34" s="3" t="n">
         <v>19.7</v>
       </c>
-      <c r="M34" s="10" t="n">
+      <c r="M34" s="13" t="n">
         <v>1.9</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>8.1</v>
+        <v>87.2</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="Q34" s="3" t="n">
-        <v>27.8</v>
-      </c>
-      <c r="R34" s="3" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Q34" s="8" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="R34" s="8" t="n">
         <v>20.9</v>
       </c>
       <c r="S34" s="3" t="n">
         <v>22.3</v>
       </c>
       <c r="T34" s="3" t="n">
-        <v>61.2</v>
+        <v>67.2</v>
       </c>
       <c r="U34" s="3" t="n">
-        <v>23.9</v>
-      </c>
-      <c r="V34" s="3" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="V34" s="8" t="n">
         <v>20</v>
       </c>
-      <c r="W34" s="11" t="n">
+      <c r="W34" s="8" t="n">
         <v>21.5</v>
       </c>
       <c r="X34" s="3" t="n">
         <v>86.3</v>
       </c>
       <c r="Y34" s="3" t="n">
-        <v>6.2</v>
+        <v>6.7</v>
       </c>
       <c r="Z34" s="3" t="n">
         <v>9</v>
@@ -3334,16 +3334,16 @@
         </is>
       </c>
       <c r="C35" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="D35" s="3" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="D35" s="8" t="n">
         <v>30.4</v>
       </c>
-      <c r="E35" s="3" t="n">
-        <v>19.4</v>
-      </c>
-      <c r="F35" s="3" t="n">
-        <v>27.4</v>
+      <c r="E35" s="8" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="F35" s="8" t="n">
+        <v>24.4</v>
       </c>
       <c r="G35" s="3" t="n">
         <v>12</v>
@@ -3357,43 +3357,43 @@
       <c r="J35" s="3" t="n">
         <v>2.9</v>
       </c>
-      <c r="K35" s="3" t="n">
+      <c r="K35" s="8" t="n">
         <v>1.6</v>
       </c>
       <c r="L35" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="M35" s="10" t="n">
-        <v>1.3</v>
+      <c r="M35" s="13" t="n">
+        <v>1.9</v>
       </c>
       <c r="N35" s="3" t="n">
-        <v>1.1</v>
+        <v>28.6</v>
       </c>
       <c r="O35" s="3" t="n">
-        <v>92.40000000000001</v>
+        <v>92.2</v>
       </c>
       <c r="P35" s="3" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="Q35" s="8" t="n">
         <v>28</v>
       </c>
-      <c r="R35" s="3" t="n">
+      <c r="R35" s="8" t="n">
         <v>22.8</v>
       </c>
       <c r="S35" s="3" t="n">
         <v>24.6</v>
       </c>
       <c r="T35" s="3" t="n">
-        <v>129.2</v>
+        <v>12.2</v>
       </c>
       <c r="U35" s="3" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="V35" s="3" t="n">
-        <v>32</v>
-      </c>
-      <c r="W35" s="11" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="V35" s="8" t="n">
+        <v>22</v>
+      </c>
+      <c r="W35" s="8" t="n">
         <v>24.2</v>
       </c>
       <c r="X35" s="3" t="n">
@@ -3403,7 +3403,7 @@
         <v>13.2</v>
       </c>
       <c r="Z35" s="3" t="n">
-        <v>33.6</v>
+        <v>53.2</v>
       </c>
       <c r="AA35" s="3" t="inlineStr">
         <is>
@@ -3422,14 +3422,14 @@
       <c r="D36" s="8" t="n">
         <v>33.6</v>
       </c>
-      <c r="E36" s="3" t="n">
-        <v>19</v>
-      </c>
-      <c r="F36" s="3" t="n">
+      <c r="E36" s="8" t="n">
+        <v>18</v>
+      </c>
+      <c r="F36" s="8" t="n">
         <v>25.8</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>1.5</v>
+        <v>15.6</v>
       </c>
       <c r="H36" s="3" t="n">
         <v>15.4</v>
@@ -3440,47 +3440,47 @@
       <c r="J36" s="3" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="K36" s="3" t="n">
+      <c r="K36" s="8" t="n">
         <v>11.5</v>
       </c>
       <c r="L36" s="3" t="n">
         <v>18.7</v>
       </c>
-      <c r="M36" s="10" t="n">
-        <v>1.8</v>
+      <c r="M36" s="13" t="n">
+        <v>1.2</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0.8</v>
+        <v>8.6</v>
       </c>
       <c r="O36" s="3" t="n">
         <v>90.2</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>11</v>
-      </c>
-      <c r="Q36" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q36" s="8" t="n">
         <v>31.2</v>
       </c>
       <c r="R36" s="8" t="n">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="S36" s="3" t="n">
         <v>27.9</v>
       </c>
       <c r="T36" s="3" t="n">
-        <v>48.2</v>
+        <v>44.2</v>
       </c>
       <c r="U36" s="3" t="n">
         <v>28.3</v>
       </c>
-      <c r="V36" s="3" t="n">
+      <c r="V36" s="8" t="n">
         <v>23.9</v>
       </c>
-      <c r="W36" s="11" t="n">
+      <c r="W36" s="8" t="n">
         <v>27</v>
       </c>
       <c r="X36" s="3" t="n">
-        <v>85.2</v>
+        <v>55.2</v>
       </c>
       <c r="Y36" s="3" t="n">
         <v>11.5</v>
@@ -3502,13 +3502,13 @@
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr"/>
-      <c r="D37" s="9" t="n">
+      <c r="D37" s="8" t="n">
         <v>161.5</v>
       </c>
       <c r="E37" s="9" t="n">
-        <v>1929.5</v>
-      </c>
-      <c r="F37" s="9" t="n">
+        <v>92.5</v>
+      </c>
+      <c r="F37" s="8" t="n">
         <v>126.9</v>
       </c>
       <c r="G37" s="3" t="n">
@@ -3523,53 +3523,53 @@
       <c r="J37" s="3" t="n">
         <v>20.3</v>
       </c>
-      <c r="K37" s="9" t="n">
-        <v>949.9</v>
+      <c r="K37" s="8" t="n">
+        <v>49.1</v>
       </c>
       <c r="L37" s="9" t="n">
-        <v>951.1</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="M37" s="9" t="n">
-        <v>0.1</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="N37" s="3" t="n">
-        <v>11.7</v>
+        <v>0.8</v>
       </c>
       <c r="O37" s="3" t="n">
-        <v>150.2</v>
+        <v>150.4</v>
       </c>
       <c r="P37" s="3" t="n">
-        <v>28.6</v>
-      </c>
-      <c r="Q37" s="9" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="Q37" s="8" t="n">
         <v>142.8</v>
       </c>
-      <c r="R37" s="9" t="n">
-        <v>117.3</v>
+      <c r="R37" s="8" t="n">
+        <v>117.5</v>
       </c>
       <c r="S37" s="3" t="n">
-        <v>120.4</v>
+        <v>190.4</v>
       </c>
       <c r="T37" s="3" t="n">
-        <v>101.3</v>
+        <v>70.3</v>
       </c>
       <c r="U37" s="3" t="n">
         <v>124.7</v>
       </c>
-      <c r="V37" s="9" t="n">
-        <v>111</v>
-      </c>
-      <c r="W37" s="11" t="n">
+      <c r="V37" s="8" t="n">
+        <v>110</v>
+      </c>
+      <c r="W37" s="8" t="n">
         <v>125.9</v>
       </c>
       <c r="X37" s="3" t="n">
-        <v>7367.2</v>
+        <v>267.2</v>
       </c>
       <c r="Y37" s="3" t="n">
         <v>37.2</v>
       </c>
       <c r="Z37" s="3" t="n">
-        <v>247.3</v>
+        <v>247.2</v>
       </c>
       <c r="AA37" s="3" t="inlineStr">
         <is>
@@ -3586,13 +3586,13 @@
       </c>
       <c r="C38" s="3" t="inlineStr"/>
       <c r="D38" s="9" t="n">
-        <v>12.3</v>
+        <v>22.3</v>
       </c>
       <c r="E38" s="9" t="n">
         <v>18.4</v>
       </c>
-      <c r="F38" s="10" t="n">
-        <v>2.5</v>
+      <c r="F38" s="9" t="n">
+        <v>25.4</v>
       </c>
       <c r="G38" s="3" t="n">
         <v>13.9</v>
@@ -3606,51 +3606,53 @@
       <c r="J38" s="3" t="n">
         <v>4.1</v>
       </c>
-      <c r="K38" s="3" t="inlineStr"/>
+      <c r="K38" s="3" t="n">
+        <v>1.1</v>
+      </c>
       <c r="L38" s="9" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="M38" s="9" t="n">
-        <v>17.8</v>
+        <v>7.8</v>
       </c>
       <c r="N38" s="3" t="n">
-        <v>18.8</v>
+        <v>18.6</v>
       </c>
       <c r="O38" s="3" t="n">
         <v>90.90000000000001</v>
       </c>
       <c r="P38" s="3" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="Q38" s="9" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="Q38" s="8" t="n">
         <v>28.6</v>
       </c>
-      <c r="R38" s="9" t="n">
+      <c r="R38" s="8" t="n">
         <v>23.5</v>
       </c>
       <c r="S38" s="3" t="n">
         <v>26.1</v>
       </c>
       <c r="T38" s="3" t="n">
-        <v>4.9</v>
+        <v>49.2</v>
       </c>
       <c r="U38" s="3" t="n">
         <v>24.9</v>
       </c>
-      <c r="V38" s="9" t="n">
-        <v>82.2</v>
-      </c>
-      <c r="W38" s="11" t="n">
+      <c r="V38" s="8" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="W38" s="8" t="n">
         <v>25.2</v>
       </c>
       <c r="X38" s="3" t="n">
-        <v>13.2</v>
+        <v>73.2</v>
       </c>
       <c r="Y38" s="3" t="n">
-        <v>2.4</v>
+        <v>7.6</v>
       </c>
       <c r="Z38" s="3" t="n">
-        <v>14.9</v>
+        <v>14.1</v>
       </c>
       <c r="AA38" s="3" t="inlineStr">
         <is>
@@ -3669,7 +3671,7 @@
       <c r="D39" s="3" t="n">
         <v>32.6</v>
       </c>
-      <c r="E39" s="10" t="n">
+      <c r="E39" s="13" t="n">
         <v>45.3</v>
       </c>
       <c r="F39" s="3" t="n">
@@ -3678,7 +3680,7 @@
       <c r="G39" s="3" t="n">
         <v>45.4</v>
       </c>
-      <c r="H39" s="8" t="n">
+      <c r="H39" s="3" t="n">
         <v>17</v>
       </c>
       <c r="I39" s="3" t="n">
@@ -3687,18 +3689,18 @@
       <c r="J39" s="3" t="n">
         <v>2.9</v>
       </c>
-      <c r="K39" s="3" t="n">
-        <v>60.2</v>
-      </c>
-      <c r="L39" s="10" t="n">
-        <v>49</v>
+      <c r="K39" s="8" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="L39" s="3" t="n">
+        <v>19</v>
       </c>
       <c r="M39" s="3" t="n">
-        <v>19.8</v>
+        <v>19</v>
       </c>
       <c r="N39" s="3" t="inlineStr"/>
       <c r="O39" s="3" t="n">
-        <v>79.59999999999999</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="P39" s="3" t="n">
         <v>0</v>
@@ -3710,7 +3712,7 @@
         <v>22.6</v>
       </c>
       <c r="S39" s="3" t="n">
-        <v>22.1</v>
+        <v>25.1</v>
       </c>
       <c r="T39" s="3" t="n">
         <v>61.2</v>
@@ -3721,8 +3723,8 @@
       <c r="V39" s="3" t="n">
         <v>20.9</v>
       </c>
-      <c r="W39" s="10" t="n">
-        <v>2.4</v>
+      <c r="W39" s="13" t="n">
+        <v>24.1</v>
       </c>
       <c r="X39" s="3" t="n">
         <v>8.199999999999999</v>
@@ -3749,38 +3751,38 @@
       <c r="C40" s="3" t="n">
         <v>1.1</v>
       </c>
-      <c r="D40" s="11" t="n">
+      <c r="D40" s="8" t="n">
         <v>32.5</v>
       </c>
-      <c r="E40" s="11" t="n">
+      <c r="E40" s="8" t="n">
         <v>18.3</v>
       </c>
-      <c r="F40" s="11" t="n">
+      <c r="F40" s="8" t="n">
         <v>25.4</v>
       </c>
       <c r="G40" s="3" t="n">
         <v>14.2</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>18.8</v>
+        <v>18</v>
       </c>
       <c r="I40" s="3" t="n">
         <v>2.9</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>51</v>
-      </c>
-      <c r="K40" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="K40" s="8" t="n">
         <v>0</v>
       </c>
       <c r="L40" s="3" t="n">
         <v>18.9</v>
       </c>
-      <c r="M40" s="10" t="n">
-        <v>1.8</v>
+      <c r="M40" s="3" t="n">
+        <v>18.2</v>
       </c>
       <c r="N40" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>29.8</v>
       </c>
       <c r="O40" s="3" t="n">
         <v>92.2</v>
@@ -3789,7 +3791,7 @@
         <v>0.2</v>
       </c>
       <c r="Q40" s="3" t="n">
-        <v>21.8</v>
+        <v>31.2</v>
       </c>
       <c r="R40" s="3" t="n">
         <v>28.2</v>
@@ -3801,7 +3803,7 @@
         <v>47.2</v>
       </c>
       <c r="U40" s="3" t="n">
-        <v>1.9</v>
+        <v>19.6</v>
       </c>
       <c r="V40" s="3" t="n">
         <v>22.8</v>
@@ -3816,7 +3818,7 @@
         <v>2.6</v>
       </c>
       <c r="Z40" s="3" t="n">
-        <v>826.2</v>
+        <v>26.9</v>
       </c>
       <c r="AA40" s="3" t="inlineStr">
         <is>
@@ -3832,17 +3834,17 @@
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr"/>
-      <c r="D41" s="11" t="n">
+      <c r="D41" s="8" t="n">
         <v>31.8</v>
       </c>
-      <c r="E41" s="11" t="n">
+      <c r="E41" s="8" t="n">
         <v>19</v>
       </c>
-      <c r="F41" s="11" t="n">
+      <c r="F41" s="8" t="n">
         <v>25.4</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>12.8</v>
+        <v>82.8</v>
       </c>
       <c r="H41" s="3" t="n">
         <v>17</v>
@@ -3851,26 +3853,26 @@
         <v>0.3</v>
       </c>
       <c r="J41" s="3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="K41" s="3" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="K41" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="L41" s="8" t="n">
-        <v>9.1</v>
+      <c r="L41" s="3" t="n">
+        <v>20.1</v>
       </c>
       <c r="M41" s="3" t="n">
         <v>20</v>
       </c>
       <c r="N41" s="3" t="inlineStr"/>
       <c r="O41" s="3" t="n">
-        <v>81.2</v>
+        <v>91.2</v>
       </c>
       <c r="P41" s="3" t="n">
-        <v>1.6</v>
+        <v>0.2</v>
       </c>
       <c r="Q41" s="3" t="n">
-        <v>29.4</v>
+        <v>24.1</v>
       </c>
       <c r="R41" s="3" t="n">
         <v>22.8</v>
@@ -3879,7 +3881,7 @@
         <v>27</v>
       </c>
       <c r="T41" s="3" t="n">
-        <v>37.8</v>
+        <v>59.2</v>
       </c>
       <c r="U41" s="3" t="n">
         <v>9</v>
@@ -3891,13 +3893,13 @@
         <v>24.2</v>
       </c>
       <c r="X41" s="3" t="n">
-        <v>8.199999999999999</v>
+        <v>82.2</v>
       </c>
       <c r="Y41" s="3" t="n">
         <v>2.6</v>
       </c>
       <c r="Z41" s="3" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="AA41" s="3" t="inlineStr">
         <is>
@@ -3913,7 +3915,7 @@
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr"/>
-      <c r="D42" s="13" t="inlineStr"/>
+      <c r="D42" s="12" t="inlineStr"/>
       <c r="E42" s="3" t="n">
         <v>18.8</v>
       </c>
@@ -3924,25 +3926,25 @@
         <v>25.6</v>
       </c>
       <c r="H42" s="3" t="n">
-        <v>1.3</v>
+        <v>13.6</v>
       </c>
       <c r="I42" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="J42" s="8" t="n">
-        <v>72.8</v>
-      </c>
-      <c r="K42" s="3" t="n">
+      <c r="J42" s="3" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="K42" s="8" t="n">
         <v>1.5</v>
       </c>
       <c r="L42" s="3" t="n">
-        <v>18.4</v>
+        <v>19.4</v>
       </c>
       <c r="M42" s="3" t="n">
-        <v>13.3</v>
+        <v>19.3</v>
       </c>
       <c r="N42" s="3" t="n">
-        <v>0.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="O42" s="3" t="n">
         <v>92.2</v>
@@ -3950,26 +3952,26 @@
       <c r="P42" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q42" s="10" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="R42" s="10" t="n">
-        <v>82</v>
+      <c r="Q42" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>22</v>
       </c>
       <c r="S42" s="3" t="n">
         <v>24.6</v>
       </c>
       <c r="T42" s="3" t="n">
-        <v>11.6</v>
+        <v>14.2</v>
       </c>
       <c r="U42" s="3" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="V42" s="10" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="W42" s="10" t="n">
-        <v>0.7</v>
+        <v>3.6</v>
+      </c>
+      <c r="V42" s="13" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="W42" s="13" t="n">
+        <v>0.2</v>
       </c>
       <c r="X42" s="3" t="inlineStr"/>
       <c r="Y42" s="3" t="inlineStr"/>
@@ -3990,26 +3992,26 @@
       <c r="C43" s="3" t="n">
         <v>0.1</v>
       </c>
-      <c r="D43" s="13" t="inlineStr"/>
-      <c r="E43" s="13" t="inlineStr"/>
-      <c r="F43" s="13" t="inlineStr"/>
+      <c r="D43" s="12" t="inlineStr"/>
+      <c r="E43" s="12" t="inlineStr"/>
+      <c r="F43" s="12" t="inlineStr"/>
       <c r="G43" s="3" t="inlineStr"/>
       <c r="H43" s="3" t="inlineStr"/>
       <c r="I43" s="3" t="inlineStr"/>
       <c r="J43" s="3" t="inlineStr"/>
-      <c r="K43" s="13" t="inlineStr"/>
-      <c r="L43" s="13" t="inlineStr"/>
-      <c r="M43" s="13" t="inlineStr"/>
+      <c r="K43" s="8" t="inlineStr"/>
+      <c r="L43" s="12" t="inlineStr"/>
+      <c r="M43" s="12" t="inlineStr"/>
       <c r="N43" s="3" t="inlineStr"/>
       <c r="O43" s="3" t="inlineStr"/>
       <c r="P43" s="3" t="inlineStr"/>
-      <c r="Q43" s="13" t="inlineStr"/>
-      <c r="R43" s="13" t="inlineStr"/>
+      <c r="Q43" s="12" t="inlineStr"/>
+      <c r="R43" s="12" t="inlineStr"/>
       <c r="S43" s="3" t="inlineStr"/>
       <c r="T43" s="3" t="inlineStr"/>
       <c r="U43" s="3" t="inlineStr"/>
-      <c r="V43" s="13" t="inlineStr"/>
-      <c r="W43" s="13" t="inlineStr"/>
+      <c r="V43" s="12" t="inlineStr"/>
+      <c r="W43" s="12" t="inlineStr"/>
       <c r="X43" s="3" t="inlineStr"/>
       <c r="Y43" s="3" t="inlineStr"/>
       <c r="Z43" s="3" t="inlineStr"/>
@@ -4029,26 +4031,26 @@
       <c r="C44" s="3" t="n">
         <v>0.1</v>
       </c>
-      <c r="D44" s="13" t="inlineStr"/>
-      <c r="E44" s="13" t="inlineStr"/>
-      <c r="F44" s="13" t="inlineStr"/>
+      <c r="D44" s="12" t="inlineStr"/>
+      <c r="E44" s="12" t="inlineStr"/>
+      <c r="F44" s="12" t="inlineStr"/>
       <c r="G44" s="3" t="inlineStr"/>
       <c r="H44" s="3" t="inlineStr"/>
       <c r="I44" s="3" t="inlineStr"/>
       <c r="J44" s="3" t="inlineStr"/>
-      <c r="K44" s="13" t="inlineStr"/>
-      <c r="L44" s="13" t="inlineStr"/>
-      <c r="M44" s="13" t="inlineStr"/>
+      <c r="K44" s="8" t="inlineStr"/>
+      <c r="L44" s="12" t="inlineStr"/>
+      <c r="M44" s="12" t="inlineStr"/>
       <c r="N44" s="3" t="inlineStr"/>
       <c r="O44" s="3" t="inlineStr"/>
       <c r="P44" s="3" t="inlineStr"/>
-      <c r="Q44" s="13" t="inlineStr"/>
-      <c r="R44" s="13" t="inlineStr"/>
+      <c r="Q44" s="12" t="inlineStr"/>
+      <c r="R44" s="12" t="inlineStr"/>
       <c r="S44" s="3" t="inlineStr"/>
       <c r="T44" s="3" t="inlineStr"/>
       <c r="U44" s="3" t="inlineStr"/>
-      <c r="V44" s="13" t="inlineStr"/>
-      <c r="W44" s="13" t="inlineStr"/>
+      <c r="V44" s="12" t="inlineStr"/>
+      <c r="W44" s="12" t="inlineStr"/>
       <c r="X44" s="3" t="inlineStr"/>
       <c r="Y44" s="3" t="inlineStr"/>
       <c r="Z44" s="3" t="inlineStr"/>
@@ -4070,7 +4072,7 @@
         <v>122.3</v>
       </c>
       <c r="E45" s="9" t="n">
-        <v>24.6</v>
+        <v>34.6</v>
       </c>
       <c r="F45" s="9" t="n">
         <v>102</v>
@@ -4085,20 +4087,20 @@
         <v>9.1</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="K45" s="9" t="n">
-        <v>8.800000000000001</v>
+        <v>15.6</v>
+      </c>
+      <c r="K45" s="8" t="n">
+        <v>7.7</v>
       </c>
       <c r="L45" s="9" t="n">
-        <v>111.4</v>
+        <v>14.6</v>
       </c>
       <c r="M45" s="9" t="n">
-        <v>111.9</v>
+        <v>11.1</v>
       </c>
       <c r="N45" s="3" t="inlineStr"/>
       <c r="O45" s="3" t="n">
-        <v>2366.2</v>
+        <v>26.6</v>
       </c>
       <c r="P45" s="3" t="n">
         <v>0.6</v>
@@ -4113,25 +4115,25 @@
         <v>241.2</v>
       </c>
       <c r="T45" s="3" t="n">
-        <v>132.7</v>
+        <v>38.7</v>
       </c>
       <c r="U45" s="3" t="n">
-        <v>1.8</v>
+        <v>96.3</v>
       </c>
       <c r="V45" s="9" t="n">
-        <v>892.7</v>
+        <v>85.7</v>
       </c>
       <c r="W45" s="9" t="n">
         <v>96.3</v>
       </c>
       <c r="X45" s="3" t="n">
-        <v>19327.2</v>
+        <v>327.2</v>
       </c>
       <c r="Y45" s="3" t="n">
-        <v>21.4</v>
+        <v>21.7</v>
       </c>
       <c r="Z45" s="3" t="n">
-        <v>8.199999999999999</v>
+        <v>82.2</v>
       </c>
       <c r="AA45" s="3" t="inlineStr">
         <is>
@@ -4147,14 +4149,14 @@
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr"/>
-      <c r="D46" s="10" t="n">
-        <v>1.1</v>
+      <c r="D46" s="13" t="n">
+        <v>0.1</v>
       </c>
       <c r="E46" s="9" t="n">
         <v>32.3</v>
       </c>
-      <c r="F46" s="10" t="n">
-        <v>1.8</v>
+      <c r="F46" s="9" t="n">
+        <v>18.7</v>
       </c>
       <c r="G46" s="3" t="n">
         <v>25.5</v>
@@ -4163,28 +4165,28 @@
         <v>17.5</v>
       </c>
       <c r="I46" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="J46" s="8" t="n">
-        <v>30.7</v>
+        <v>2.3</v>
+      </c>
+      <c r="J46" s="3" t="n">
+        <v>13.7</v>
       </c>
       <c r="K46" s="3" t="n">
-        <v>0.4</v>
+        <v>9.9</v>
       </c>
       <c r="L46" s="9" t="n">
-        <v>92.40000000000001</v>
+        <v>12.4</v>
       </c>
       <c r="M46" s="9" t="n">
         <v>19.9</v>
       </c>
       <c r="N46" s="3" t="n">
-        <v>22.8</v>
+        <v>22.3</v>
       </c>
       <c r="O46" s="3" t="n">
-        <v>92.3</v>
+        <v>92.2</v>
       </c>
       <c r="P46" s="3" t="n">
-        <v>2.6</v>
+        <v>26.7</v>
       </c>
       <c r="Q46" s="9" t="n">
         <v>0.2</v>
@@ -4196,23 +4198,25 @@
         <v>22.9</v>
       </c>
       <c r="T46" s="3" t="n">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="U46" s="3" t="n">
-        <v>22.8</v>
+        <v>29.8</v>
       </c>
       <c r="V46" s="9" t="n">
         <v>21.4</v>
       </c>
       <c r="W46" s="9" t="n">
-        <v>2.4</v>
+        <v>24.1</v>
       </c>
       <c r="X46" s="3" t="n">
         <v>60.2</v>
       </c>
-      <c r="Y46" s="3" t="inlineStr"/>
+      <c r="Y46" s="3" t="n">
+        <v>2.1</v>
+      </c>
       <c r="Z46" s="3" t="n">
-        <v>992.9</v>
+        <v>298.9</v>
       </c>
       <c r="AA46" s="3" t="inlineStr">
         <is>
